--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484253_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484253_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>P. MARTINEZ ALEJANO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,40 +565,40 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0773</v>
+        <v>3.2596</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7127</v>
+        <v>4.4873</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.6354</v>
+        <v>-1.2277</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4845</v>
+        <v>-2.7081</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2709</v>
+        <v>-2.1428</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2136</v>
+        <v>-0.5653</v>
       </c>
       <c r="J2" t="n">
-        <v>4.011</v>
+        <v>0.2328</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9877</v>
+        <v>-0.2814</v>
       </c>
       <c r="L2" t="n">
-        <v>2.0233</v>
+        <v>0.5142</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.5265</v>
+        <v>-2.9409</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7168</v>
+        <v>-1.8613</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8097</v>
+        <v>-1.0795</v>
       </c>
       <c r="P2" t="n">
         <v>0.7814</v>
@@ -610,28 +610,28 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2461</v>
+        <v>0.965</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9053</v>
+        <v>0.7437</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6593</v>
+        <v>0.2213</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5654</v>
+        <v>4.2213</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7731</v>
+        <v>4.4876</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2077</v>
+        <v>-0.2663</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9638</v>
+        <v>2.918</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2865</v>
+        <v>5.3083</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2504</v>
+        <v>-2.3903</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0531</v>
+        <v>1.4845</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3492</v>
+        <v>0.2709</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2961</v>
+        <v>1.2136</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9204</v>
+        <v>4.011</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7585</v>
+        <v>1.9877</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1619</v>
+        <v>2.0233</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9735</v>
+        <v>-2.5265</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1077</v>
+        <v>-1.7168</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1342</v>
+        <v>-0.8097</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8422</v>
+        <v>0.0867</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0851</v>
+        <v>0.5009</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9273</v>
+        <v>-0.4142</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1747</v>
+        <v>0.5654</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8317</v>
+        <v>1.7731</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3431</v>
+        <v>-1.2077</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. MARTINEZ ALEJANO</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6275</v>
+        <v>2.7091</v>
       </c>
       <c r="E4" t="n">
-        <v>3.719</v>
+        <v>-0.0238</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0916</v>
+        <v>2.7329</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.7081</v>
+        <v>-0.0531</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1428</v>
+        <v>-0.3492</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5653</v>
+        <v>0.2961</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2328</v>
+        <v>0.9204</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2814</v>
+        <v>0.7585</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5142</v>
+        <v>0.1619</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9409</v>
+        <v>-0.9735</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8613</v>
+        <v>-1.1077</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0795</v>
+        <v>0.1342</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3329</v>
+        <v>1.5875</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0246</v>
+        <v>0.1776</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3575</v>
+        <v>1.4099</v>
       </c>
       <c r="V4" t="n">
-        <v>4.2213</v>
+        <v>1.1747</v>
       </c>
       <c r="W4" t="n">
-        <v>4.4876</v>
+        <v>0.8317</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2663</v>
+        <v>0.3431</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.713</v>
+        <v>0.4369</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6885</v>
+        <v>2.3852</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9755</v>
+        <v>-1.9483</v>
       </c>
       <c r="G5" t="n">
         <v>0.5443</v>
@@ -844,13 +844,13 @@
         <v>0.586</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2273</v>
+        <v>-0.0488</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7484</v>
+        <v>0.4451</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5211</v>
+        <v>-0.4939</v>
       </c>
       <c r="V5" t="n">
         <v>0.3321</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4106</v>
+        <v>0.1617</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5411</v>
+        <v>-0.8445</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9517</v>
+        <v>1.0061</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4599</v>
@@ -922,13 +922,13 @@
         <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.3198</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0689</v>
+        <v>-0.2345</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1398</v>
+        <v>-0.0854</v>
       </c>
       <c r="V6" t="n">
         <v>0.9414</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1062</v>
+        <v>0.1398</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9876</v>
+        <v>0.6627</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0937</v>
+        <v>-0.5229</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6248</v>
+        <v>0.3535</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3287</v>
+        <v>0.2853</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2961</v>
+        <v>0.0683</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6554</v>
+        <v>0.9776</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0069</v>
+        <v>1.0438</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6484</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.2802</v>
+        <v>-0.6241</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.3356</v>
+        <v>-0.7585</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9445</v>
+        <v>0.1344</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8357</v>
+        <v>-0.0853</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1888</v>
+        <v>-0.3149</v>
       </c>
       <c r="U7" t="n">
-        <v>0.647</v>
+        <v>0.2297</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8317</v>
+        <v>-1.4959</v>
       </c>
       <c r="W7" t="n">
-        <v>2.0503</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.362</v>
+        <v>-0.4658</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4605</v>
+        <v>1.8459</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8225</v>
+        <v>-2.3116</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3535</v>
+        <v>-0.6248</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2853</v>
+        <v>-0.3287</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0683</v>
+        <v>-0.2961</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9776</v>
+        <v>2.6554</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0438</v>
+        <v>2.0069</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.06610000000000001</v>
+        <v>0.6484</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6241</v>
+        <v>-3.2802</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7585</v>
+        <v>-2.3356</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1344</v>
+        <v>-0.9445</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3674</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5871</v>
+        <v>1.4761</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5172</v>
+        <v>1.047</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0699</v>
+        <v>0.4291</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4959</v>
+        <v>0.8317</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.0503</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7805</v>
+        <v>-1.7182</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.436</v>
+        <v>-2.5371</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6555</v>
+        <v>0.8189</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8546</v>
@@ -1156,13 +1156,13 @@
         <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7225</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2504</v>
+        <v>0.1493</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4721</v>
+        <v>0.6355</v>
       </c>
       <c r="V9" t="n">
         <v>0.1097</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7609</v>
+        <v>-3.4709</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9341</v>
+        <v>-0.6713</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8268</v>
+        <v>-2.7996</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7899</v>
@@ -1234,13 +1234,13 @@
         <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0286</v>
+        <v>0.2614</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2062</v>
+        <v>0.0566</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1776</v>
+        <v>0.2048</v>
       </c>
       <c r="V10" t="n">
         <v>0.011</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3376</v>
+        <v>-4.4697</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5778</v>
+        <v>-2.9823</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7598</v>
+        <v>-1.4875</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6287</v>
@@ -1312,13 +1312,13 @@
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3853</v>
+        <v>0.2532</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3385</v>
+        <v>-0.0659</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0467</v>
+        <v>0.3191</v>
       </c>
       <c r="V11" t="n">
         <v>-2.0942</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0664</v>
+        <v>-4.8193</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5726</v>
+        <v>-0.1076</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.4938</v>
+        <v>-4.7116</v>
       </c>
       <c r="G12" t="n">
         <v>0.9482</v>
@@ -1390,13 +1390,13 @@
         <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7901</v>
+        <v>1.0372</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3548</v>
+        <v>0.1102</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1449</v>
+        <v>0.927</v>
       </c>
       <c r="V12" t="n">
         <v>-4.2652</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6214</v>
+        <v>-5.318800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>7.2202</v>
+        <v>7.5228</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.8415</v>
+        <v>-12.8416</v>
       </c>
       <c r="G13" t="n">
         <v>-5.788600000000001</v>
@@ -1468,16 +1468,16 @@
         <v>15.6274</v>
       </c>
       <c r="S13" t="n">
-        <v>5.6954</v>
+        <v>5.997999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3124</v>
+        <v>2.6151</v>
       </c>
       <c r="U13" t="n">
-        <v>3.383</v>
+        <v>3.3829</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3319999999999999</v>
+        <v>0.3320000000000007</v>
       </c>
       <c r="W13" t="n">
         <v>13.6851</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8016</v>
+        <v>3.7111</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3898</v>
+        <v>3.448</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5882</v>
+        <v>0.2631</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9843</v>
+        <v>1.6278</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7826</v>
+        <v>1.9383</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2017</v>
+        <v>-0.3105</v>
       </c>
       <c r="J14" t="n">
-        <v>2.497</v>
+        <v>2.8717</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2947</v>
+        <v>2.9112</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2023</v>
+        <v>-0.0395</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5127</v>
+        <v>-1.2439</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5121</v>
+        <v>-0.9729</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.271</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>3.7115</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4815</v>
+        <v>-1.1707</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8778</v>
+        <v>-0.4621</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3963</v>
+        <v>-0.7086</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1638</v>
+        <v>1.4959</v>
       </c>
       <c r="W14" t="n">
         <v>2.9917</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.8279</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0329</v>
+        <v>3.1598</v>
       </c>
       <c r="E15" t="n">
-        <v>3.448</v>
+        <v>4.8843</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4151</v>
+        <v>-1.7244</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6278</v>
+        <v>0.9843</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9383</v>
+        <v>0.7826</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3105</v>
+        <v>0.2017</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8717</v>
+        <v>2.497</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9112</v>
+        <v>2.2947</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0395</v>
+        <v>0.2023</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2439</v>
+        <v>-1.5127</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9729</v>
+        <v>-1.5121</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.271</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>3.7115</v>
+        <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8489</v>
+        <v>-0.1603</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4621</v>
+        <v>0.3722</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.3868</v>
+        <v>-0.5325</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4959</v>
+        <v>1.1638</v>
       </c>
       <c r="W15" t="n">
         <v>2.9917</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4959</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7073</v>
+        <v>1.5433</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6882</v>
+        <v>2.554</v>
       </c>
       <c r="F16" t="n">
-        <v>0.019</v>
+        <v>-1.0107</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0059</v>
+        <v>1.1815</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5598</v>
+        <v>-2.0417</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5538999999999999</v>
+        <v>3.2232</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3795</v>
+        <v>2.5596</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2581</v>
+        <v>-0.5296</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1214</v>
+        <v>3.0892</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3737</v>
+        <v>-1.3781</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6984</v>
+        <v>-1.5121</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6753</v>
+        <v>0.134</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4353</v>
+        <v>-0.4196</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0384</v>
+        <v>-0.2475</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.397</v>
+        <v>-0.1721</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6572</v>
+        <v>1.4142</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8963</v>
+        <v>1.5871</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2392</v>
+        <v>-0.173</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7972</v>
+        <v>3.0059</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3671</v>
+        <v>3.5598</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4301</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3339</v>
+        <v>4.3795</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4981</v>
+        <v>4.2581</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8358</v>
+        <v>0.1214</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5366</v>
+        <v>-1.3737</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.131</v>
+        <v>-0.6984</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4056</v>
+        <v>-0.6753</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>3.3208</v>
+        <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5894</v>
+        <v>-0.7285</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2805</v>
+        <v>-0.1395</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3089</v>
+        <v>-0.589</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9414</v>
+        <v>-0.2772</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7731</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.7145</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4893</v>
+        <v>0.8386</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1496</v>
+        <v>2.9974</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6603</v>
+        <v>-2.1588</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1815</v>
+        <v>1.7972</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0417</v>
+        <v>0.3671</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2232</v>
+        <v>1.4301</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5596</v>
+        <v>4.3339</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5296</v>
+        <v>2.4981</v>
       </c>
       <c r="L18" t="n">
-        <v>3.0892</v>
+        <v>1.8358</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3781</v>
+        <v>-2.5366</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5121</v>
+        <v>-2.131</v>
       </c>
       <c r="O18" t="n">
-        <v>0.134</v>
+        <v>-0.4056</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>3.3208</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4736</v>
+        <v>-0.4079</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.652</v>
+        <v>-0.1794</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8217</v>
+        <v>-0.2285</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>1.7731</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1782</v>
+        <v>-0.3028</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0135</v>
+        <v>-1.0988</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1917</v>
+        <v>0.796</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0027</v>
+        <v>0.5196</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2589</v>
+        <v>0.8439</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2562</v>
+        <v>-0.3243</v>
       </c>
       <c r="J19" t="n">
-        <v>1.091</v>
+        <v>0.7396</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4298</v>
+        <v>1.3328</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6613</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0937</v>
+        <v>-0.22</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6887</v>
+        <v>-0.4889</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4051</v>
+        <v>0.2688</v>
       </c>
       <c r="P19" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5157</v>
+        <v>-0.0764</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6219</v>
+        <v>-1.0488</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1062</v>
+        <v>0.9724</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8865</v>
+        <v>-0.9414</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>1.1638</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1638</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5088</v>
+        <v>-0.3615</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1999</v>
+        <v>-1.6093</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6911</v>
+        <v>1.2479</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5196</v>
+        <v>-1.157</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8439</v>
+        <v>-1.2917</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3243</v>
+        <v>0.1346</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7396</v>
+        <v>-1.2868</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3328</v>
+        <v>-1.2868</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.22</v>
+        <v>0.1298</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4889</v>
+        <v>-0.0049</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2688</v>
+        <v>0.1346</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2824</v>
+        <v>-0.2593</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1499</v>
+        <v>-0.3225</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8676</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9414</v>
+        <v>0.6642</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1052</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.626</v>
+        <v>-0.4723</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7105</v>
+        <v>0.2046</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0844</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.157</v>
+        <v>-0.0027</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2917</v>
+        <v>-0.2589</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1346</v>
+        <v>0.2562</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2868</v>
+        <v>1.091</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2868</v>
+        <v>0.4298</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.6613</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1298</v>
+        <v>-1.0937</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0049</v>
+        <v>-0.6887</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1346</v>
+        <v>-0.4051</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5238</v>
+        <v>0.2215</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4237</v>
+        <v>-0.187</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1002</v>
+        <v>0.4085</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6642</v>
+        <v>-0.8865</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6642</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3745</v>
+        <v>-0.5901</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7846</v>
+        <v>1.189</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1591</v>
+        <v>-1.7792</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5164</v>
@@ -2170,13 +2170,13 @@
         <v>2.5395</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7762</v>
+        <v>-0.9918</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0289</v>
+        <v>-0.6244</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7474</v>
+        <v>-0.3674</v>
       </c>
       <c r="V22" t="n">
         <v>0.3321</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3793</v>
+        <v>-1.2966</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6181</v>
+        <v>-1.3147</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2387</v>
+        <v>0.0181</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6517</v>
@@ -2248,13 +2248,13 @@
         <v>1.9534</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2371</v>
+        <v>0.3198</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.544</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0844</v>
+        <v>0.8638</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9414</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.621499999999999</v>
+        <v>7.643700000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>12.8415</v>
+        <v>12.8416</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.2204</v>
+        <v>-5.1979</v>
       </c>
       <c r="G24" t="n">
         <v>5.7885</v>
@@ -2326,16 +2326,16 @@
         <v>21.4878</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.6953</v>
+        <v>-3.6732</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.3831</v>
+        <v>-3.383</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.3125</v>
+        <v>-0.2901999999999997</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3318999999999999</v>
+        <v>-0.3319000000000003</v>
       </c>
       <c r="W24" t="n">
         <v>13.353</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484253_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484253_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>-0.2663</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.918</v>
+        <v>2.7091</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3083</v>
+        <v>-0.0238</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3903</v>
+        <v>2.7329</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4845</v>
+        <v>-0.0531</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2709</v>
+        <v>-0.3492</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2136</v>
+        <v>0.2961</v>
       </c>
       <c r="J3" t="n">
-        <v>4.011</v>
+        <v>0.9204</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9877</v>
+        <v>0.7585</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0233</v>
+        <v>0.1619</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5265</v>
+        <v>-0.9735</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7168</v>
+        <v>-1.1077</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8097</v>
+        <v>0.1342</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0867</v>
+        <v>1.5875</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5009</v>
+        <v>0.1776</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4142</v>
+        <v>1.4099</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5654</v>
+        <v>1.1747</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7731</v>
+        <v>0.8317</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2077</v>
+        <v>0.3431</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7091</v>
+        <v>2.004</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0238</v>
+        <v>4.3943</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7329</v>
+        <v>-2.3903</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0531</v>
+        <v>0.5705</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3492</v>
+        <v>-0.0361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2961</v>
+        <v>0.6066</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9204</v>
+        <v>3.097</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7585</v>
+        <v>1.6807</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1619</v>
+        <v>1.4163</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9735</v>
+        <v>-2.5265</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1077</v>
+        <v>-1.7168</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1342</v>
+        <v>-0.8097</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5875</v>
+        <v>0.0867</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1776</v>
+        <v>0.5009</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4099</v>
+        <v>-0.4142</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1747</v>
+        <v>0.5654</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8317</v>
+        <v>1.7731</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3431</v>
+        <v>-1.2077</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4369</v>
+        <v>0.914</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3852</v>
+        <v>0.914</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9483</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5443</v>
+        <v>0.914</v>
       </c>
       <c r="H5" t="n">
-        <v>1.583</v>
+        <v>0.307</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0387</v>
+        <v>0.607</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6982</v>
+        <v>0.914</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6577</v>
+        <v>0.307</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0405</v>
+        <v>0.607</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1538</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0747</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0792</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0488</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4451</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4939</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1617</v>
+        <v>0.4369</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8445</v>
+        <v>2.3852</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0061</v>
+        <v>-1.9483</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4599</v>
+        <v>0.5443</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2556</v>
+        <v>1.583</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7957</v>
+        <v>-1.0387</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0895</v>
+        <v>1.6982</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2459</v>
+        <v>1.6577</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3354</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5494</v>
+        <v>-1.1538</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0097</v>
+        <v>-0.0747</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5397</v>
+        <v>-1.0792</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3198</v>
+        <v>-0.0488</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2345</v>
+        <v>0.4451</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0854</v>
+        <v>-0.4939</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9414</v>
+        <v>0.3321</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6642</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1398</v>
+        <v>0.1617</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6627</v>
+        <v>-0.8445</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5229</v>
+        <v>1.0061</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3535</v>
+        <v>-0.4599</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2853</v>
+        <v>-1.2556</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0683</v>
+        <v>0.7957</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9776</v>
+        <v>0.0895</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0438</v>
+        <v>-1.2459</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.06610000000000001</v>
+        <v>1.3354</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6241</v>
+        <v>-0.5494</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7585</v>
+        <v>-0.0097</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1344</v>
+        <v>-0.5397</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0853</v>
+        <v>-0.3198</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3149</v>
+        <v>-0.2345</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2297</v>
+        <v>-0.0854</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4959</v>
+        <v>0.9414</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4959</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4658</v>
+        <v>0.1398</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8459</v>
+        <v>0.6627</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3116</v>
+        <v>-0.5229</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6248</v>
+        <v>0.3535</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3287</v>
+        <v>0.2853</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2961</v>
+        <v>0.0683</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6554</v>
+        <v>0.9776</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0069</v>
+        <v>1.0438</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6484</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.2802</v>
+        <v>-0.6241</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.3356</v>
+        <v>-0.7585</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9445</v>
+        <v>0.1344</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4761</v>
+        <v>-0.0853</v>
       </c>
       <c r="T8" t="n">
-        <v>1.047</v>
+        <v>-0.3149</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4291</v>
+        <v>0.2297</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8317</v>
+        <v>-1.4959</v>
       </c>
       <c r="W8" t="n">
-        <v>2.0503</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7182</v>
+        <v>-0.4658</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5371</v>
+        <v>1.8459</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8189</v>
+        <v>-2.3116</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8546</v>
+        <v>-0.6248</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.3287</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1082</v>
+        <v>-0.2961</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2437</v>
+        <v>2.6554</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0819</v>
+        <v>2.0069</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1619</v>
+        <v>0.6484</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0984</v>
+        <v>-3.2802</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8283</v>
+        <v>-2.3356</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.27</v>
+        <v>-0.9445</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7581</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>-3.9069</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7848000000000001</v>
+        <v>1.4761</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1493</v>
+        <v>1.047</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6355</v>
+        <v>0.4291</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1097</v>
+        <v>0.8317</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.0503</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1097</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4709</v>
+        <v>-1.7182</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6713</v>
+        <v>-2.5371</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7996</v>
+        <v>0.8189</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7899</v>
+        <v>-0.8546</v>
       </c>
       <c r="H10" t="n">
-        <v>0.921</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.7108</v>
+        <v>-0.1082</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7417</v>
+        <v>0.2437</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6426</v>
+        <v>0.0819</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9009</v>
+        <v>0.1619</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5316</v>
+        <v>-1.0984</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7217</v>
+        <v>-0.8283</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8099</v>
+        <v>-0.27</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9534</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2614</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0566</v>
+        <v>0.1493</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2048</v>
+        <v>0.6355</v>
       </c>
       <c r="V10" t="n">
-        <v>0.011</v>
+        <v>0.1097</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4263</v>
+        <v>0.1097</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4697</v>
+        <v>-3.4709</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9823</v>
+        <v>-0.6713</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4875</v>
+        <v>-2.7996</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6287</v>
+        <v>-1.7899</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6465</v>
+        <v>0.921</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9822</v>
+        <v>-2.7108</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9396</v>
+        <v>0.7417</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0422</v>
+        <v>2.6426</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9818</v>
+        <v>-1.9009</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6891</v>
+        <v>-2.5316</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6887</v>
+        <v>-1.7217</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0004</v>
+        <v>-0.8099</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2532</v>
+        <v>0.2614</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0659</v>
+        <v>0.0566</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3191</v>
+        <v>0.2048</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.0942</v>
+        <v>0.011</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.0942</v>
+        <v>-2.4263</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>J. CANAL FERRER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8193</v>
+        <v>-4.4697</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1076</v>
+        <v>-2.9823</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.7116</v>
+        <v>-1.4875</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9482</v>
+        <v>-2.6287</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6851</v>
+        <v>-0.6465</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6332</v>
+        <v>-1.9822</v>
       </c>
       <c r="J12" t="n">
-        <v>3.0797</v>
+        <v>-1.9396</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3111</v>
+        <v>0.0422</v>
       </c>
       <c r="L12" t="n">
-        <v>1.7686</v>
+        <v>-1.9818</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1316</v>
+        <v>-0.6891</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.9962</v>
+        <v>-0.6887</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1354</v>
+        <v>-0.0004</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.5395</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0372</v>
+        <v>0.2532</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1102</v>
+        <v>-0.0659</v>
       </c>
       <c r="U12" t="n">
-        <v>0.927</v>
+        <v>0.3191</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.2652</v>
+        <v>-2.0942</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.8745</v>
+        <v>-2.0942</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.318800000000001</v>
+        <v>-4.8193</v>
       </c>
       <c r="E13" t="n">
-        <v>7.5228</v>
+        <v>-0.1076</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.8416</v>
+        <v>-4.7116</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.788600000000001</v>
+        <v>0.9482</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.0942</v>
+        <v>-0.6851</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.694399999999999</v>
+        <v>1.6332</v>
       </c>
       <c r="J13" t="n">
-        <v>12.7104</v>
+        <v>3.0797</v>
       </c>
       <c r="K13" t="n">
-        <v>10.0051</v>
+        <v>1.3111</v>
       </c>
       <c r="L13" t="n">
-        <v>2.7054</v>
+        <v>1.7686</v>
       </c>
       <c r="M13" t="n">
-        <v>-18.4991</v>
+        <v>-2.1316</v>
       </c>
       <c r="N13" t="n">
-        <v>-13.0992</v>
+        <v>-1.9962</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.399699999999999</v>
+        <v>-0.1354</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.860300000000001</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q13" t="n">
-        <v>-21.4877</v>
+        <v>-3.9069</v>
       </c>
       <c r="R13" t="n">
-        <v>15.6274</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>5.997999999999999</v>
+        <v>1.0372</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6151</v>
+        <v>0.1102</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3829</v>
+        <v>0.927</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3320000000000007</v>
+        <v>-4.2652</v>
       </c>
       <c r="W13" t="n">
-        <v>13.6851</v>
+        <v>0.6093</v>
       </c>
       <c r="X13" t="n">
-        <v>-13.353</v>
+        <v>-4.8745</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7111</v>
+        <v>-5.318799999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>3.448</v>
+        <v>7.5228</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2631</v>
+        <v>-12.8416</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6278</v>
+        <v>-5.788600000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9383</v>
+        <v>-3.0942</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3105</v>
+        <v>-2.6944</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8717</v>
+        <v>12.7104</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9112</v>
+        <v>10.0051</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0395</v>
+        <v>2.7054</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2439</v>
+        <v>-18.4991</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9729</v>
+        <v>-13.0992</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.271</v>
+        <v>-5.3997</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7581</v>
+        <v>-5.860300000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-21.4877</v>
       </c>
       <c r="R14" t="n">
-        <v>3.7115</v>
+        <v>15.6274</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1707</v>
+        <v>5.997999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4621</v>
+        <v>2.6151</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7086</v>
+        <v>3.3829</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4959</v>
+        <v>0.3320000000000016</v>
       </c>
       <c r="W14" t="n">
-        <v>2.9917</v>
+        <v>13.6851</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4959</v>
-      </c>
+        <v>-13.353</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1598</v>
+        <v>3.7111</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8843</v>
+        <v>3.448</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7244</v>
+        <v>0.2631</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9843</v>
+        <v>1.6278</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7826</v>
+        <v>1.9383</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2017</v>
+        <v>-0.3105</v>
       </c>
       <c r="J15" t="n">
-        <v>2.497</v>
+        <v>2.8717</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2947</v>
+        <v>2.9112</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2023</v>
+        <v>-0.0395</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5127</v>
+        <v>-1.2439</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5121</v>
+        <v>-0.9729</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.271</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>3.7115</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1603</v>
+        <v>-1.1707</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3722</v>
+        <v>-0.4621</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5325</v>
+        <v>-0.7086</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1638</v>
+        <v>1.4959</v>
       </c>
       <c r="W15" t="n">
         <v>2.9917</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8279</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5433</v>
+        <v>3.1598</v>
       </c>
       <c r="E16" t="n">
-        <v>2.554</v>
+        <v>4.8843</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0107</v>
+        <v>-1.7244</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1815</v>
+        <v>0.9843</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.0417</v>
+        <v>0.7826</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2232</v>
+        <v>0.2017</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5596</v>
+        <v>2.497</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5296</v>
+        <v>2.2947</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0892</v>
+        <v>0.2023</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3781</v>
+        <v>-1.5127</v>
       </c>
       <c r="N16" t="n">
         <v>-1.5121</v>
       </c>
       <c r="O16" t="n">
-        <v>0.134</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4196</v>
+        <v>-0.1603</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2475</v>
+        <v>0.3722</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1721</v>
+        <v>-0.5325</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>2.9917</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4142</v>
+        <v>1.5433</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5871</v>
+        <v>2.554</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.173</v>
+        <v>-1.0107</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0059</v>
+        <v>1.1815</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5598</v>
+        <v>-2.0417</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5538999999999999</v>
+        <v>3.2232</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3795</v>
+        <v>2.5596</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2581</v>
+        <v>-0.5296</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1214</v>
+        <v>3.0892</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3737</v>
+        <v>-1.3781</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6984</v>
+        <v>-1.5121</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6753</v>
+        <v>0.134</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7285</v>
+        <v>-0.4196</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1395</v>
+        <v>-0.2475</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.589</v>
+        <v>-0.1721</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8386</v>
+        <v>1.4142</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9974</v>
+        <v>1.5871</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1588</v>
+        <v>-0.173</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7972</v>
+        <v>3.0059</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3671</v>
+        <v>3.5598</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4301</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>4.3339</v>
+        <v>4.3795</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4981</v>
+        <v>4.2581</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8358</v>
+        <v>0.1214</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5366</v>
+        <v>-1.3737</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.131</v>
+        <v>-0.6984</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4056</v>
+        <v>-0.6753</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>3.3208</v>
+        <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4079</v>
+        <v>-0.7285</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1794</v>
+        <v>-0.1395</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2285</v>
+        <v>-0.589</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9414</v>
+        <v>-0.2772</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7731</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.7145</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3028</v>
+        <v>0.8386</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0988</v>
+        <v>2.9974</v>
       </c>
       <c r="F19" t="n">
-        <v>0.796</v>
+        <v>-2.1588</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5196</v>
+        <v>1.7972</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8439</v>
+        <v>0.3671</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3243</v>
+        <v>1.4301</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7396</v>
+        <v>4.3339</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3328</v>
+        <v>2.4981</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5931999999999999</v>
+        <v>1.8358</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.22</v>
+        <v>-2.5366</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4889</v>
+        <v>-2.131</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2688</v>
+        <v>-0.4056</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1488</v>
+        <v>3.3208</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0764</v>
+        <v>-0.4079</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0488</v>
+        <v>-0.1794</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9724</v>
+        <v>-0.2285</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9414</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1638</v>
+        <v>1.7731</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1052</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3615</v>
+        <v>-0.3028</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6093</v>
+        <v>-1.0988</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2479</v>
+        <v>0.796</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.157</v>
+        <v>0.5196</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2917</v>
+        <v>0.8439</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1346</v>
+        <v>-0.3243</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2868</v>
+        <v>0.7396</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2868</v>
+        <v>1.3328</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1298</v>
+        <v>-0.22</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0049</v>
+        <v>-0.4889</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1346</v>
+        <v>0.2688</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2593</v>
+        <v>-0.0764</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3225</v>
+        <v>-1.0488</v>
       </c>
       <c r="U20" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.9724</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6642</v>
+        <v>-0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6642</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4723</v>
+        <v>-0.3615</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2046</v>
+        <v>-1.6093</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6768999999999999</v>
+        <v>1.2479</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0027</v>
+        <v>-1.157</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2589</v>
+        <v>-1.2917</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2562</v>
+        <v>0.1346</v>
       </c>
       <c r="J21" t="n">
-        <v>1.091</v>
+        <v>-1.2868</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4298</v>
+        <v>-1.2868</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6613</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0937</v>
+        <v>0.1298</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6887</v>
+        <v>-0.0049</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4051</v>
+        <v>0.1346</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2215</v>
+        <v>-0.2593</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.187</v>
+        <v>-0.3225</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4085</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8865</v>
+        <v>0.6642</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1638</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5901</v>
+        <v>-0.4723</v>
       </c>
       <c r="E22" t="n">
-        <v>1.189</v>
+        <v>0.2046</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7792</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5164</v>
+        <v>-0.0027</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3336</v>
+        <v>-0.2589</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.85</v>
+        <v>0.2562</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6617</v>
+        <v>1.091</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0271</v>
+        <v>0.4298</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6613</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1781</v>
+        <v>-1.0937</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6935</v>
+        <v>-0.6887</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4846</v>
+        <v>-0.4051</v>
       </c>
       <c r="P22" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9918</v>
+        <v>0.2215</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6244</v>
+        <v>-0.187</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3674</v>
+        <v>0.4085</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3321</v>
+        <v>-0.8865</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1052</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7731</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2966</v>
+        <v>-0.5901</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3147</v>
+        <v>1.189</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0181</v>
+        <v>-1.7792</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6517</v>
+        <v>-0.5164</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1389</v>
+        <v>0.3336</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5128</v>
+        <v>-0.85</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3485</v>
+        <v>1.6617</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1637</v>
+        <v>1.0271</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5122</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3032</v>
+        <v>-2.1781</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3026</v>
+        <v>-0.6935</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-1.4846</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9534</v>
+        <v>2.5395</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3198</v>
+        <v>-0.9918</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.544</v>
+        <v>-0.6244</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8638</v>
+        <v>-0.3674</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9414</v>
+        <v>0.3321</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5545</v>
+        <v>2.1052</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4959</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,152 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-1.2966</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.3147</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.6517</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.1389</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.5128</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.3485</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.5122</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.3032</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.3026</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.544</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.8638</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.9414</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484253_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>7.643700000000001</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E25" t="n">
         <v>12.8416</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F25" t="n">
         <v>-5.1979</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G25" t="n">
         <v>5.7885</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H25" t="n">
         <v>3.0941</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>2.6943</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>18.4987</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K25" t="n">
         <v>13.0991</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L25" t="n">
         <v>5.3997</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M25" t="n">
         <v>-12.7102</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N25" t="n">
         <v>-10.0051</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O25" t="n">
         <v>-2.7054</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P25" t="n">
         <v>5.860300000000001</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q25" t="n">
         <v>-15.6272</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>21.4878</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>-3.6732</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>-3.383</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>-0.2901999999999997</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V25" t="n">
         <v>-0.3319000000000003</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W25" t="n">
         <v>13.353</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X25" t="n">
         <v>-13.6852</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
